--- a/FigafJiraIntegration/IntegrationFlow/Update_Jira_Issues/Documentation.xlsx
+++ b/FigafJiraIntegration/IntegrationFlow/Update_Jira_Issues/Documentation.xlsx
@@ -407,7 +407,7 @@
     <t>Address</t>
   </si>
   <si>
-    <t>sampledev(cpi-trial-alex)-&gt;sampleqa(cpi-trial-alex)</t>
+    <t>sampledev(trial-cpi-alex)-&gt;sampleqa(trial-cpi-alex)</t>
   </si>
   <si>
     <t>sampledev</t>
